--- a/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -94,64 +94,94 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>MONT</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CLEMENTE</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>BRAVO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>GARNICA</t>
+  </si>
+  <si>
+    <t>LARA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>CANUTO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>CRISTIAN FERMIN</t>
-  </si>
-  <si>
-    <t>ISRAEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>LEONARDO GAEL</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
     <t>JESUS ANTONIO</t>
   </si>
   <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
     <t>DIEGO</t>
   </si>
   <si>
     <t>CLAUDIA</t>
   </si>
   <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>JESUS SAMUEL</t>
+    <t>IRVING JAIR</t>
   </si>
 </sst>
 </file>
@@ -552,19 +582,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>71.43000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -604,16 +634,16 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
         <v>6.8</v>
@@ -799,16 +829,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="E2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>78.56999999999999</v>
+      </c>
+      <c r="H2">
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -822,16 +855,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="E3">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H3">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -845,16 +881,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>33.33</v>
+      </c>
+      <c r="H4">
+        <v>7.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -868,16 +907,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>54.84</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -891,16 +933,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>47.62</v>
+      </c>
+      <c r="H6">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -937,16 +982,19 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="E8">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F8">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>47.62</v>
+      </c>
+      <c r="H8">
+        <v>7.3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1022,19 +1070,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>71.43000000000001</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1051,16 +1099,16 @@
         <v>1</v>
       </c>
       <c r="E3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>64.29000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1074,19 +1122,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1112,7 +1160,7 @@
         <v>77.42</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1129,16 +1177,16 @@
         <v>1</v>
       </c>
       <c r="E6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G6">
-        <v>47.62</v>
+        <v>57.14</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1181,16 +1229,16 @@
         <v>3</v>
       </c>
       <c r="E8">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G8">
-        <v>57.14</v>
+        <v>61.9</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1226,7 +1274,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1258,16 +1306,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920121</v>
+        <v>21330051920127</v>
       </c>
       <c r="B2" t="s">
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1276,21 +1324,21 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920121</v>
+        <v>21330051920127</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1299,168 +1347,214 @@
         <v>12</v>
       </c>
       <c r="G3">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920073</v>
+        <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G4">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>19330051920314</v>
+        <v>20330051920213</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920326</v>
+        <v>20330051920264</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920118</v>
+        <v>20330051920320</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G7">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920122</v>
+        <v>20330051920326</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G8">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920268</v>
+        <v>21330051920117</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920323</v>
+        <v>21330051920118</v>
       </c>
       <c r="B10" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>12</v>
+      </c>
+      <c r="G10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920122</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>19330051920238</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
         <v>44</v>
       </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>17</v>
-      </c>
-      <c r="G10">
-        <v>6</v>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,9 @@
     <t>MONT</t>
   </si>
   <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
@@ -155,6 +158,9 @@
   </si>
   <si>
     <t>PAUL ADRIAN</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
   </si>
   <si>
     <t>REYNA ARISBETH</t>
@@ -855,19 +861,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3">
-        <v>50</v>
+        <v>53.57</v>
       </c>
       <c r="H3">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -933,19 +939,19 @@
         <v>21</v>
       </c>
       <c r="D6">
+        <v>9</v>
+      </c>
+      <c r="E6">
+        <v>9</v>
+      </c>
+      <c r="F6">
         <v>11</v>
       </c>
-      <c r="E6">
-        <v>10</v>
-      </c>
-      <c r="F6">
-        <v>10</v>
-      </c>
       <c r="G6">
-        <v>47.62</v>
+        <v>52.38</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -959,16 +965,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="E7">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>82.86</v>
+      </c>
+      <c r="H7">
+        <v>8.4</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1186,7 +1195,7 @@
         <v>57.14</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1203,16 +1212,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1274,7 +1283,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1312,10 +1321,10 @@
         <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1335,10 +1344,10 @@
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1352,30 +1361,30 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920190</v>
+        <v>20330051920087</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920213</v>
+        <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
@@ -1384,7 +1393,7 @@
         <v>37</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1398,7 +1407,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920264</v>
+        <v>20330051920213</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -1407,21 +1416,21 @@
         <v>38</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920320</v>
+        <v>20330051920264</v>
       </c>
       <c r="B7" t="s">
         <v>29</v>
@@ -1430,21 +1439,21 @@
         <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920326</v>
+        <v>20330051920320</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
@@ -1453,7 +1462,7 @@
         <v>40</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1467,7 +1476,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920117</v>
+        <v>20330051920326</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1476,21 +1485,21 @@
         <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G9">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920118</v>
+        <v>21330051920117</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -1499,7 +1508,7 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1513,7 +1522,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920122</v>
+        <v>21330051920118</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
@@ -1522,7 +1531,7 @@
         <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E11" t="s">
         <v>9</v>
@@ -1531,12 +1540,12 @@
         <v>12</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920238</v>
+        <v>21330051920122</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -1545,15 +1554,38 @@
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
+        <v>12</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>19330051920238</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
         <v>15</v>
       </c>
-      <c r="G12">
+      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
@@ -109,24 +109,24 @@
     <t>CLEMENTE</t>
   </si>
   <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>ENCARNACION</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>BRAVO</t>
   </si>
   <si>
@@ -139,24 +139,24 @@
     <t>GARNICA</t>
   </si>
   <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>VILLA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>LARA</t>
   </si>
   <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>PAUL ADRIAN</t>
   </si>
   <si>
@@ -172,22 +172,22 @@
     <t>LEONARDO GAEL</t>
   </si>
   <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>DIANA IRAIS</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>CLAUDIA</t>
+  </si>
+  <si>
+    <t>IRVING JAIR</t>
+  </si>
+  <si>
     <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
   </si>
 </sst>
 </file>
@@ -1017,16 +1017,19 @@
         <v>31</v>
       </c>
       <c r="D9">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="F9">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G9">
-        <v>0</v>
+        <v>96.77</v>
+      </c>
+      <c r="H9">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -1273,7 +1276,7 @@
         <v>96.77</v>
       </c>
       <c r="H9">
-        <v>8.5</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1367,7 +1370,7 @@
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
         <v>47</v>
@@ -1448,12 +1451,12 @@
         <v>15</v>
       </c>
       <c r="G7">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920320</v>
+        <v>20330051920326</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
@@ -1476,7 +1479,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920326</v>
+        <v>21330051920117</v>
       </c>
       <c r="B9" t="s">
         <v>31</v>
@@ -1488,18 +1491,18 @@
         <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920117</v>
+        <v>21330051920118</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -1522,7 +1525,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920118</v>
+        <v>21330051920122</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
@@ -1540,12 +1543,12 @@
         <v>12</v>
       </c>
       <c r="G11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920122</v>
+        <v>19330051920238</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
@@ -1557,18 +1560,18 @@
         <v>55</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920238</v>
+        <v>20330051920320</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
@@ -1583,7 +1586,7 @@
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G13">
         <v>1</v>

--- a/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -92,102 +92,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MONT</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CLEMENTE</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>ENCARNACION</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>BRAVO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>GARNICA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>VILLA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>PAUL ADRIAN</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>LEONARDO GAEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>DIANA IRAIS</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>CLAUDIA</t>
-  </si>
-  <si>
-    <t>IRVING JAIR</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
   </si>
 </sst>
 </file>
@@ -588,19 +492,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -614,19 +518,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>9</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>64.29000000000001</v>
+        <v>67.86</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -640,19 +544,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>7</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -666,19 +570,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G5">
-        <v>77.42</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -692,19 +596,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>10</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
-        <v>47.62</v>
+        <v>52.38</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -744,19 +648,19 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>6</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G8">
-        <v>57.14</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H8">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -835,19 +739,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -861,19 +765,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>53.57</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -887,19 +791,19 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="G4">
-        <v>33.33</v>
+        <v>96.97</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -913,19 +817,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>54.84</v>
+        <v>96.77</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -939,19 +843,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>52.38</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -965,19 +869,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="G7">
-        <v>82.86</v>
+        <v>97.14</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -991,19 +895,19 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F8">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="G8">
-        <v>47.62</v>
+        <v>90.48</v>
       </c>
       <c r="H8">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1082,19 +986,19 @@
         <v>28</v>
       </c>
       <c r="D2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>78.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.3</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1108,19 +1012,19 @@
         <v>28</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>67.86</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1134,16 +1038,16 @@
         <v>33</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="G4">
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="H4">
         <v>6.9</v>
@@ -1160,19 +1064,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>77.42</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1186,19 +1090,19 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="G6">
-        <v>57.14</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1215,16 +1119,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G7">
-        <v>88.56999999999999</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1238,19 +1142,19 @@
         <v>21</v>
       </c>
       <c r="D8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G8">
-        <v>61.9</v>
+        <v>100</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1267,16 +1171,16 @@
         <v>0</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G9">
-        <v>96.77</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1286,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1316,282 +1220,6 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920127</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920127</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" t="s">
-        <v>46</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>12</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>20330051920087</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920190</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920213</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920264</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920326</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
-        <v>51</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920117</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D9" t="s">
-        <v>52</v>
-      </c>
-      <c r="E9" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" t="s">
-        <v>12</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920118</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10" t="s">
-        <v>53</v>
-      </c>
-      <c r="E10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F10" t="s">
-        <v>12</v>
-      </c>
-      <c r="G10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920122</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" t="s">
-        <v>54</v>
-      </c>
-      <c r="E11" t="s">
-        <v>9</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>19330051920238</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>15</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>20330051920320</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>17</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
+++ b/docentes/González Nuñez Veronica - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -92,6 +92,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>ZUNO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>URIEL ALFREDO</t>
   </si>
 </sst>
 </file>
@@ -1093,16 +1102,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1190,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1220,6 +1229,29 @@
         <v>24</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>19330051920425</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
